--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY2"/>
+  <dimension ref="A1:DY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,10 +1080,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2025</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -1466,10 +1464,8 @@
         <v>0</v>
       </c>
       <c r="DV2" t="inlineStr"/>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>5.68</t>
-        </is>
+      <c r="DW2" t="n">
+        <v>5.68</v>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
@@ -1479,6 +1475,409 @@
       <c r="DY2" t="inlineStr">
         <is>
           <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>45680.91666666666</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14</v>
+      </c>
+      <c r="W3" t="n">
+        <v>11</v>
+      </c>
+      <c r="X3" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Caseros</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Avenida General Justo José de Urquiza y Lisandro de la Torre, Caseros, Provincia de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>710</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>69</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>89</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>10</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>31</v>
+      </c>
+      <c r="DO3" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP3" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY3"/>
+  <dimension ref="A1:DY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1479,10 +1479,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2025</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -1865,10 +1863,8 @@
         <v>0</v>
       </c>
       <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
+      <c r="DW3" t="n">
+        <v>11.5</v>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
@@ -1878,6 +1874,409 @@
       <c r="DY3" t="inlineStr">
         <is>
           <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45704.83333333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>15</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X4" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Estadio Marcelo Alberto Bielsa</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Parque de la Independencia, Barrio Centro, Rosario, Provincia de Santa Fe</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>710</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>88</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>19</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>18</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>17</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>84</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>31</v>
+      </c>
+      <c r="DO4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY4"/>
+  <dimension ref="A1:DY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1878,10 +1878,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2025</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
@@ -2264,10 +2262,8 @@
         <v>1</v>
       </c>
       <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="DW4" t="n">
+        <v>4</v>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
@@ -2279,6 +2275,397 @@
           <t>20%</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45746</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>13</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>17</v>
+      </c>
+      <c r="W5" t="n">
+        <v>12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Antonio Vespucio Liberti</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Avenida Presidente José Figueroa Alcorta 7597, Núñez, Capital Federal, Ciudad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>68</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>25</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>12</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>9</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>33</v>
+      </c>
+      <c r="DO5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY5"/>
+  <dimension ref="A1:DY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,174 +2283,174 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45712.83333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U5" t="n">
+        <v>15</v>
+      </c>
+      <c r="V5" t="n">
         <v>11</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>45746</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>13</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>20</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>17</v>
-      </c>
       <c r="W5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X5" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Estadio Monumental Antonio Vespucio Liberti</t>
+          <t>Estadio Claudio Chiqui Tapia</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Avenida Presidente José Figueroa Alcorta 7597, Núñez, Capital Federal, Ciudad de Buenos Aires</t>
+          <t>Avenida Olavaría 3400 y Luna, Bairro Barracas, Capital Federal, Ciudad de Buenos Aires</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
         <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>3.9</v>
       </c>
-      <c r="AF5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AR5" t="n">
-        <v>2.69</v>
+        <v>2.26</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1</v>
+        <v>750</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -2465,181 +2465,181 @@
         <v>1</v>
       </c>
       <c r="BH5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK5" t="n">
         <v>3</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1</v>
-      </c>
       <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
         <v>5</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS5" t="n">
         <v>3</v>
       </c>
-      <c r="BN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1</v>
-      </c>
       <c r="BT5" t="n">
         <v>1</v>
       </c>
       <c r="BU5" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="BV5" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="BW5" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="BX5" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>14</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>13</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>59</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA5" t="n">
         <v>42</v>
       </c>
-      <c r="BY5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>12</v>
-      </c>
-      <c r="CU5" t="n">
+      <c r="DB5" t="n">
+        <v>84</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>42</v>
+      </c>
+      <c r="DJ5" t="n">
         <v>17</v>
       </c>
-      <c r="CV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>6</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>17</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>37</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>9</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>35</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>84</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>64</v>
-      </c>
       <c r="DK5" t="n">
-        <v>1.83</v>
+        <v>0.92</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.93</v>
+        <v>2.12</v>
       </c>
       <c r="DN5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="DO5" t="b">
         <v>1</v>
@@ -2648,10 +2648,10 @@
         <v>1</v>
       </c>
       <c r="DQ5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS5" t="b">
         <v>0</v>
@@ -2660,13 +2660,402 @@
         <v>0</v>
       </c>
       <c r="DU5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="inlineStr"/>
       <c r="DW5" t="inlineStr"/>
       <c r="DX5" t="inlineStr"/>
       <c r="DY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45746</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>13</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>20</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Antonio Vespucio Liberti</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Avenida Presidente José Figueroa Alcorta 7597, Núñez, Capital Federal, Ciudad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>68</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>6</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>9</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>33</v>
+      </c>
+      <c r="DO6" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP6" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ6" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR6" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV6" t="inlineStr"/>
+      <c r="DW6" t="inlineStr"/>
+      <c r="DX6" t="inlineStr"/>
+      <c r="DY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY6"/>
+  <dimension ref="A1:DY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1878,157 +1878,159 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2025</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45681.92708333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Newell's Old Boys</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>45704.83333333334</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
       <c r="V4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
         <v>18</v>
       </c>
       <c r="X4" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Estadio Marcelo Alberto Bielsa</t>
+          <t>Estadio Libertadores de América</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Parque de la Independencia, Barrio Centro, Rosario, Provincia de Santa Fe</t>
+          <t>Calle Ricardo Enrique Bochini (ex. Almirante Cordero) 751/83 esq. Alsina, Avellaneda, Provincia de Buenos Aires</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.53</v>
+        <v>6.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AJ4" t="n">
         <v>2.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AT4" t="n">
         <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
@@ -2043,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
@@ -2064,37 +2066,37 @@
         <v>1</v>
       </c>
       <c r="BH4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BI4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS4" t="n">
         <v>4</v>
@@ -2103,37 +2105,37 @@
         <v>1</v>
       </c>
       <c r="BU4" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BV4" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="BW4" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="BX4" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2154,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
@@ -2169,73 +2171,73 @@
         <v>1</v>
       </c>
       <c r="CQ4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CR4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CS4" t="n">
         <v>1</v>
       </c>
       <c r="CT4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CU4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CV4" t="n">
         <v>1</v>
       </c>
       <c r="CW4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CX4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CY4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DA4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DD4" t="n">
         <v>1.13</v>
       </c>
-      <c r="DD4" t="n">
-        <v>2</v>
-      </c>
       <c r="DE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="DN4" t="n">
         <v>31</v>
@@ -2262,8 +2264,10 @@
         <v>1</v>
       </c>
       <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="n">
-        <v>4</v>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
@@ -2272,49 +2276,47 @@
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2025</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45712.83333333334</v>
+        <v>45704.83333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -2332,40 +2334,40 @@
         <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
+        <v>9</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" t="n">
         <v>15</v>
       </c>
-      <c r="V5" t="n">
-        <v>11</v>
-      </c>
       <c r="W5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="X5" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="Y5" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Estadio Claudio Chiqui Tapia</t>
+          <t>Estadio Marcelo Alberto Bielsa</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Avenida Olavaría 3400 y Luna, Bairro Barracas, Capital Federal, Ciudad de Buenos Aires</t>
+          <t>Parque de la Independencia, Barrio Centro, Rosario, Provincia de Santa Fe</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -2375,82 +2377,82 @@
         <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ5" t="n">
         <v>1</v>
       </c>
       <c r="BA5" t="n">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -2465,64 +2467,64 @@
         <v>1</v>
       </c>
       <c r="BH5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BM5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ5" t="n">
         <v>2</v>
       </c>
       <c r="BR5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT5" t="n">
         <v>1</v>
       </c>
       <c r="BU5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BV5" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="BW5" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="BX5" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.82</v>
+        <v>0.9</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.27</v>
+        <v>2.87</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2549,13 +2551,13 @@
         <v>1</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
@@ -2570,73 +2572,73 @@
         <v>1</v>
       </c>
       <c r="CQ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>18</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX5" t="n">
         <v>12</v>
       </c>
-      <c r="CR5" t="n">
-        <v>12</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>14</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>13</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>9</v>
-      </c>
       <c r="CY5" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="CZ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>17</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DI5" t="n">
         <v>84</v>
       </c>
-      <c r="DA5" t="n">
-        <v>42</v>
-      </c>
-      <c r="DB5" t="n">
+      <c r="DJ5" t="n">
         <v>84</v>
       </c>
-      <c r="DC5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>42</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>17</v>
-      </c>
       <c r="DK5" t="n">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.12</v>
+        <v>2.84</v>
       </c>
       <c r="DN5" t="n">
         <v>31</v>
@@ -2648,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="DQ5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR5" t="b">
         <v>0</v>
@@ -2660,186 +2662,196 @@
         <v>0</v>
       </c>
       <c r="DU5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
-      <c r="DY5" t="inlineStr"/>
+      <c r="DW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2025</v>
       </c>
       <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45712.83333333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>15</v>
+      </c>
+      <c r="V6" t="n">
         <v>11</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>45746</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>13</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8</v>
-      </c>
-      <c r="V6" t="n">
-        <v>17</v>
-      </c>
       <c r="W6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X6" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Estadio Monumental Antonio Vespucio Liberti</t>
+          <t>Estadio Claudio Chiqui Tapia</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Avenida Presidente José Figueroa Alcorta 7597, Núñez, Capital Federal, Ciudad de Buenos Aires</t>
+          <t>Avenida Olavaría 3400 y Luna, Bairro Barracas, Capital Federal, Ciudad de Buenos Aires</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
         <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>3.9</v>
       </c>
-      <c r="AF6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AR6" t="n">
-        <v>2.69</v>
+        <v>2.26</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA6" t="n">
-        <v>-1</v>
+        <v>750</v>
       </c>
       <c r="BB6" t="n">
         <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -2854,181 +2866,181 @@
         <v>1</v>
       </c>
       <c r="BH6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>2</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
         <v>5</v>
       </c>
-      <c r="BM6" t="n">
-        <v>3</v>
-      </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
         <v>1</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT6" t="n">
         <v>1</v>
       </c>
       <c r="BU6" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="BV6" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="BW6" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="BX6" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>14</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>13</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>59</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA6" t="n">
         <v>42</v>
       </c>
-      <c r="BY6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>12</v>
-      </c>
-      <c r="CU6" t="n">
+      <c r="DB6" t="n">
+        <v>84</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>42</v>
+      </c>
+      <c r="DJ6" t="n">
         <v>17</v>
       </c>
-      <c r="CV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>6</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>17</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>37</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>35</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>84</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>64</v>
-      </c>
       <c r="DK6" t="n">
-        <v>1.83</v>
+        <v>0.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="DM6" t="n">
-        <v>2.93</v>
+        <v>2.12</v>
       </c>
       <c r="DN6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="DO6" t="b">
         <v>1</v>
@@ -3037,10 +3049,10 @@
         <v>1</v>
       </c>
       <c r="DQ6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="b">
         <v>0</v>
@@ -3049,13 +3061,402 @@
         <v>0</v>
       </c>
       <c r="DU6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="inlineStr"/>
       <c r="DW6" t="inlineStr"/>
       <c r="DX6" t="inlineStr"/>
       <c r="DY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45746</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>13</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>17</v>
+      </c>
+      <c r="W7" t="n">
+        <v>12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Antonio Vespucio Liberti</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Avenida Presidente José Figueroa Alcorta 7597, Núñez, Capital Federal, Ciudad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>68</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>85</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>12</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>6</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>9</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>33</v>
+      </c>
+      <c r="DO7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY7"/>
+  <dimension ref="A1:EG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,6 +1078,46 @@
           <t>clouds</t>
         </is>
       </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over25</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over15</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over35</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_2</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_1</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_x</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_btts_yes</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_btts_no</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1477,6 +1517,14 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1876,12 +1924,18 @@
           <t>40%</t>
         </is>
       </c>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2025</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -2264,10 +2318,8 @@
         <v>1</v>
       </c>
       <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
+      <c r="DW4" t="n">
+        <v>6.06</v>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
@@ -2279,6 +2331,14 @@
           <t>25%</t>
         </is>
       </c>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2678,6 +2738,14 @@
           <t>20%</t>
         </is>
       </c>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3067,6 +3135,14 @@
       <c r="DW6" t="inlineStr"/>
       <c r="DX6" t="inlineStr"/>
       <c r="DY6" t="inlineStr"/>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr"/>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
+      <c r="EG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3456,6 +3532,457 @@
       <c r="DW7" t="inlineStr"/>
       <c r="DX7" t="inlineStr"/>
       <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Talleres Córdoba</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45878.01041666666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>704</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>39</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>33</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>11</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>31</v>
+      </c>
+      <c r="DO8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EG8"/>
+  <dimension ref="A1:EM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1116,36 @@
       <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_btts_no</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over05</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under05</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_over_85</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_under_85</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_under_95</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_over_95</t>
         </is>
       </c>
     </row>
@@ -1525,6 +1555,12 @@
       <c r="EE2" t="inlineStr"/>
       <c r="EF2" t="inlineStr"/>
       <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1932,6 +1968,12 @@
       <c r="EE3" t="inlineStr"/>
       <c r="EF3" t="inlineStr"/>
       <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2339,6 +2381,12 @@
       <c r="EE4" t="inlineStr"/>
       <c r="EF4" t="inlineStr"/>
       <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2746,6 +2794,12 @@
       <c r="EE5" t="inlineStr"/>
       <c r="EF5" t="inlineStr"/>
       <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3143,6 +3197,12 @@
       <c r="EE6" t="inlineStr"/>
       <c r="EF6" t="inlineStr"/>
       <c r="EG6" t="inlineStr"/>
+      <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
+      <c r="EK6" t="inlineStr"/>
+      <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3540,6 +3600,12 @@
       <c r="EE7" t="inlineStr"/>
       <c r="EF7" t="inlineStr"/>
       <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+      <c r="EK7" t="inlineStr"/>
+      <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3552,40 +3618,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45878.01041666666</v>
+        <v>45876.83333333334</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3594,128 +3660,128 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
+        <v>16</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
         <v>9</v>
       </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7</v>
-      </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X8" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="Y8" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
+          <t>Estadio Malvinas Argentinas</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
+          <t>Calle San Francisco De Asis y Boulogne Sur Mer Mendoza, Mendoza, Provincia de Mendoza</t>
         </is>
       </c>
       <c r="AB8" t="n">
         <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
         <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.71</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA8" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -3730,64 +3796,64 @@
         <v>1</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL8" t="n">
         <v>3</v>
       </c>
       <c r="BM8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR8" t="n">
         <v>5</v>
       </c>
-      <c r="BN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>3</v>
-      </c>
       <c r="BS8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT8" t="n">
         <v>1</v>
       </c>
       <c r="BU8" t="n">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="BV8" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="BW8" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="BX8" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.51</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.47</v>
+        <v>3.39</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
@@ -3829,25 +3895,25 @@
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP8" t="n">
         <v>1</v>
       </c>
       <c r="CQ8" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="CR8" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="CS8" t="n">
         <v>1</v>
       </c>
       <c r="CT8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="CU8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV8" t="n">
         <v>1</v>
@@ -3856,52 +3922,52 @@
         <v>3</v>
       </c>
       <c r="CX8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="CY8" t="n">
         <v>17</v>
       </c>
       <c r="CZ8" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="DA8" t="n">
         <v>11</v>
       </c>
       <c r="DB8" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.93</v>
+        <v>0.93</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.27</v>
+        <v>0.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="DI8" t="n">
         <v>84</v>
       </c>
       <c r="DJ8" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="DK8" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="DL8" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="DM8" t="n">
-        <v>3.14</v>
+        <v>2.12</v>
       </c>
       <c r="DN8" t="n">
         <v>31</v>
@@ -3910,10 +3976,10 @@
         <v>1</v>
       </c>
       <c r="DP8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR8" t="b">
         <v>0</v>
@@ -3925,64 +3991,525 @@
         <v>0</v>
       </c>
       <c r="DU8" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Talleres Córdoba</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45878.01041666666</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>704</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>33</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>31</v>
+      </c>
+      <c r="DO9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
         <v>10.44</v>
       </c>
-      <c r="DW8" t="n">
+      <c r="DW9" t="n">
         <v>2.45</v>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="DX9" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="DY9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>7.15</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
+      <c r="DZ9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM9"/>
+  <dimension ref="A1:EM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3608,10 +3608,8 @@
       <c r="EM7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2025</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -3994,10 +3992,8 @@
         <v>1</v>
       </c>
       <c r="DV8" t="inlineStr"/>
-      <c r="DW8" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="DW8" t="n">
+        <v>5.75</v>
       </c>
       <c r="DX8" t="inlineStr">
         <is>
@@ -4009,96 +4005,70 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>4.79</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EH8" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EJ8" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EK8" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EL8" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EM8" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
+      <c r="DZ8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2025</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>45878.01041666666</v>
+        <v>45876.91666666666</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -4110,19 +4080,19 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4134,95 +4104,87 @@
         <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
         <v>8</v>
       </c>
-      <c r="T9" t="n">
-        <v>15</v>
-      </c>
-      <c r="U9" t="n">
-        <v>9</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7</v>
-      </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="X9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2</v>
-      </c>
       <c r="AO9" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
@@ -4246,7 +4208,7 @@
         <v>1</v>
       </c>
       <c r="BA9" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
@@ -4267,124 +4229,124 @@
         <v>1</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR9" t="n">
         <v>4</v>
       </c>
-      <c r="BL9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>3</v>
-      </c>
       <c r="BS9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT9" t="n">
         <v>1</v>
       </c>
       <c r="BU9" t="n">
+        <v>98</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>67</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>115</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT9" t="n">
         <v>18</v>
       </c>
-      <c r="BV9" t="n">
-        <v>43</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>100</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>116</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>33</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>6</v>
-      </c>
       <c r="CU9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV9" t="n">
         <v>1</v>
@@ -4393,52 +4355,52 @@
         <v>3</v>
       </c>
       <c r="CX9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="CY9" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="CZ9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="DA9" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="DB9" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DI9" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="DJ9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>1.52</v>
+        <v>0.95</v>
       </c>
       <c r="DM9" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="DN9" t="n">
         <v>31</v>
@@ -4464,52 +4426,523 @@
       <c r="DU9" t="b">
         <v>0</v>
       </c>
-      <c r="DV9" t="n">
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Talleres Córdoba</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45878.01041666666</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>704</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>39</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>33</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>84</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>31</v>
+      </c>
+      <c r="DO10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
         <v>10.44</v>
       </c>
-      <c r="DW9" t="n">
+      <c r="DW10" t="n">
         <v>2.45</v>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="DX10" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
+      <c r="DY10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="DZ9" t="n">
+      <c r="DZ10" t="n">
         <v>3.28</v>
       </c>
-      <c r="EA9" t="n">
+      <c r="EA10" t="n">
         <v>1.75</v>
       </c>
-      <c r="EB9" t="n">
+      <c r="EB10" t="n">
         <v>7.15</v>
       </c>
-      <c r="EC9" t="n">
+      <c r="EC10" t="n">
         <v>3.88</v>
       </c>
-      <c r="ED9" t="n">
+      <c r="ED10" t="n">
         <v>2.36</v>
       </c>
-      <c r="EE9" t="n">
+      <c r="EE10" t="n">
         <v>2.84</v>
       </c>
-      <c r="EF9" t="n">
+      <c r="EF10" t="n">
         <v>2.46</v>
       </c>
-      <c r="EG9" t="n">
+      <c r="EG10" t="n">
         <v>1.56</v>
       </c>
-      <c r="EH9" t="inlineStr"/>
-      <c r="EI9" t="inlineStr"/>
-      <c r="EJ9" t="inlineStr"/>
-      <c r="EK9" t="inlineStr"/>
-      <c r="EL9" t="inlineStr"/>
-      <c r="EM9" t="inlineStr"/>
+      <c r="EH10" t="inlineStr"/>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
+      <c r="EM10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Argentina_Primera_División_2025.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM10"/>
+  <dimension ref="A1:EM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4049,10 +4049,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2025</v>
       </c>
       <c r="B9" t="n">
         <v>4</v>
@@ -4427,10 +4425,8 @@
         <v>0</v>
       </c>
       <c r="DV9" t="inlineStr"/>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="DW9" t="n">
+        <v>5.75</v>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
@@ -4442,226 +4438,200 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="DZ9" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
-        <is>
-          <t>6.98</t>
-        </is>
-      </c>
-      <c r="EC9" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="DZ9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2025</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45878.01041666666</v>
+        <v>45877</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
         <v>7</v>
       </c>
-      <c r="K10" t="n">
-        <v>8</v>
-      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de La Plata</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Avenida 25 y 32, La Plata, Provincia de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>9</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>45</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
       <c r="AC10" t="n">
         <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="n">
         <v>3.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.71</v>
+        <v>6.49</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AK10" t="n">
         <v>1.57</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.24</v>
+        <v>2.71</v>
       </c>
       <c r="AN10" t="n">
         <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="AR10" t="n">
         <v>2.15</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4670,22 +4640,22 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA10" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -4700,249 +4670,720 @@
         <v>1</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>112</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>15</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>9</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>34</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>18</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>58</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>67</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>32</v>
+      </c>
+      <c r="DO10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>8.97</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>6.49</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="BL10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Talleres Córdoba</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45878.01041666666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Lanús - Néstor Díaz Pérez</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Calle General J. Arias y J. Héctor Guidi, Lanús, Provincia de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>704</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>39</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM11" t="n">
         <v>5</v>
       </c>
-      <c r="BN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU10" t="n">
+      <c r="BN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU11" t="n">
         <v>18</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="BV11" t="n">
         <v>43</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="BW11" t="n">
         <v>100</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="BX11" t="n">
         <v>116</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="BY11" t="n">
         <v>1.51</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="BZ11" t="n">
         <v>0.96</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CA11" t="n">
         <v>2.47</v>
       </c>
-      <c r="CB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ10" t="n">
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ11" t="n">
         <v>18</v>
       </c>
-      <c r="CR10" t="n">
+      <c r="CR11" t="n">
         <v>33</v>
       </c>
-      <c r="CS10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT10" t="n">
+      <c r="CS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT11" t="n">
         <v>6</v>
       </c>
-      <c r="CU10" t="n">
+      <c r="CU11" t="n">
         <v>7</v>
       </c>
-      <c r="CV10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX10" t="n">
+      <c r="CV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX11" t="n">
         <v>4</v>
       </c>
-      <c r="CY10" t="n">
+      <c r="CY11" t="n">
         <v>17</v>
       </c>
-      <c r="CZ10" t="n">
+      <c r="CZ11" t="n">
         <v>50</v>
       </c>
-      <c r="DA10" t="n">
+      <c r="DA11" t="n">
         <v>11</v>
       </c>
-      <c r="DB10" t="n">
+      <c r="DB11" t="n">
         <v>39</v>
       </c>
-      <c r="DC10" t="n">
+      <c r="DC11" t="n">
         <v>1.93</v>
       </c>
-      <c r="DD10" t="n">
+      <c r="DD11" t="n">
         <v>1.27</v>
       </c>
-      <c r="DE10" t="n">
+      <c r="DE11" t="n">
         <v>1.44</v>
       </c>
-      <c r="DF10" t="n">
+      <c r="DF11" t="n">
         <v>1.22</v>
       </c>
-      <c r="DG10" t="n">
+      <c r="DG11" t="n">
         <v>1.2</v>
       </c>
-      <c r="DH10" t="n">
+      <c r="DH11" t="n">
         <v>0.89</v>
       </c>
-      <c r="DI10" t="n">
+      <c r="DI11" t="n">
         <v>84</v>
       </c>
-      <c r="DJ10" t="n">
+      <c r="DJ11" t="n">
         <v>50</v>
       </c>
-      <c r="DK10" t="n">
+      <c r="DK11" t="n">
         <v>1.62</v>
       </c>
-      <c r="DL10" t="n">
+      <c r="DL11" t="n">
         <v>1.52</v>
       </c>
-      <c r="DM10" t="n">
+      <c r="DM11" t="n">
         <v>3.14</v>
       </c>
-      <c r="DN10" t="n">
+      <c r="DN11" t="n">
         <v>31</v>
       </c>
-      <c r="DO10" t="b">
-        <v>1</v>
-      </c>
-      <c r="DP10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
+      <c r="DO11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DP11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
         <v>10.44</v>
       </c>
-      <c r="DW10" t="n">
+      <c r="DW11" t="n">
         <v>2.45</v>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="DX11" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
+      <c r="DY11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="DZ10" t="n">
+      <c r="DZ11" t="n">
         <v>3.28</v>
       </c>
-      <c r="EA10" t="n">
+      <c r="EA11" t="n">
         <v>1.75</v>
       </c>
-      <c r="EB10" t="n">
+      <c r="EB11" t="n">
         <v>7.15</v>
       </c>
-      <c r="EC10" t="n">
+      <c r="EC11" t="n">
         <v>3.88</v>
       </c>
-      <c r="ED10" t="n">
+      <c r="ED11" t="n">
         <v>2.36</v>
       </c>
-      <c r="EE10" t="n">
+      <c r="EE11" t="n">
         <v>2.84</v>
       </c>
-      <c r="EF10" t="n">
+      <c r="EF11" t="n">
         <v>2.46</v>
       </c>
-      <c r="EG10" t="n">
+      <c r="EG11" t="n">
         <v>1.56</v>
       </c>
-      <c r="EH10" t="inlineStr"/>
-      <c r="EI10" t="inlineStr"/>
-      <c r="EJ10" t="inlineStr"/>
-      <c r="EK10" t="inlineStr"/>
-      <c r="EL10" t="inlineStr"/>
-      <c r="EM10" t="inlineStr"/>
+      <c r="EH11" t="inlineStr"/>
+      <c r="EI11" t="inlineStr"/>
+      <c r="EJ11" t="inlineStr"/>
+      <c r="EK11" t="inlineStr"/>
+      <c r="EL11" t="inlineStr"/>
+      <c r="EM11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
